--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-08).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-08).xlsx
@@ -912,48 +912,48 @@
   </si>
   <si>
     <t>214
-180</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>R$ 874.483,85</t>
-  </si>
-  <si>
-    <t>R$ 4.578,45
-R$ 4.667,22</t>
-  </si>
-  <si>
-    <t>(17.6%)
-(16.0%)</t>
-  </si>
-  <si>
-    <t>49.4</t>
-  </si>
-  <si>
-    <t>(18.8%)</t>
-  </si>
-  <si>
-    <t>14.3%</t>
-  </si>
-  <si>
-    <t>(34.9%)</t>
+184</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>R$ 886.845,18</t>
+  </si>
+  <si>
+    <t>R$ 4.547,92
+R$ 4.632,94</t>
+  </si>
+  <si>
+    <t>(18.0%)
+(16.5%)</t>
+  </si>
+  <si>
+    <t>49.0</t>
+  </si>
+  <si>
+    <t>(19.2%)</t>
+  </si>
+  <si>
+    <t>13.8%</t>
+  </si>
+  <si>
+    <t>(35.2%)</t>
   </si>
   <si>
     <t>3.9%</t>
   </si>
   <si>
-    <t>0.7%</t>
+    <t>0.6%</t>
   </si>
   <si>
     <t>26.4</t>
   </si>
   <si>
-    <t>75.2%</t>
-  </si>
-  <si>
-    <t>9.0%</t>
+    <t>75.3%</t>
+  </si>
+  <si>
+    <t>8.9%</t>
   </si>
   <si>
     <t>5.4</t>
@@ -971,10 +971,10 @@
     <t>73.4%</t>
   </si>
   <si>
-    <t>-R$ 31.248,71</t>
-  </si>
-  <si>
-    <t>2.97</t>
+    <t>-R$ 31.315,61</t>
+  </si>
+  <si>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -4424,7 +4424,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4460,25 +4460,59 @@
       <c t="s" r="N24" s="4">
         <v>52</v>
       </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
+      <c r="O24" s="5">
+        <v>4031</v>
+      </c>
+      <c r="P24" s="5">
+        <v>4031</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>-0.52441628617609926</v>
+      </c>
+      <c r="R24" s="7">
+        <v>43</v>
+      </c>
+      <c r="S24" s="6">
+        <v>-0.51136363636363635</v>
+      </c>
+      <c r="T24" s="6">
+        <v>0</v>
+      </c>
+      <c r="U24" s="6">
+        <v>-0.35342594889605561</v>
+      </c>
+      <c r="V24" s="6">
+        <v>0.041415157529149094</v>
+      </c>
+      <c r="W24" s="6">
+        <v>0.012437236417762343</v>
+      </c>
+      <c r="X24" s="8">
+        <v>26.399478125000002</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>0.6875</v>
+      </c>
+      <c r="Z24" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="8">
+        <v>3.1562023255813956</v>
+      </c>
+      <c r="AB24" s="8">
+        <v>6.171875</v>
+      </c>
       <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="6"/>
+      <c r="AD24" s="8">
+        <v>16.298959374999999</v>
+      </c>
+      <c r="AE24" s="6">
+        <v>0.71875</v>
+      </c>
       <c r="AF24" s="9"/>
-      <c r="AG24" s="5"/>
+      <c r="AG24" s="5">
+        <v>-66.900000000000006</v>
+      </c>
       <c r="AH24" s="10">
         <v>2</v>
       </c>
@@ -5960,7 +5994,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5996,25 +6030,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>3057.5500000000002</v>
+      </c>
+      <c r="P36" s="5">
+        <v>3057.5500000000002</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>-0.15732829897475464</v>
+      </c>
+      <c r="R36" s="7">
+        <v>30</v>
+      </c>
+      <c r="S36" s="6">
+        <v>-0.11764705882352944</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.32367735605304898</v>
+      </c>
+      <c r="U36" s="6">
+        <v>-0.014223904760347336</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.059418652188844005</v>
+      </c>
+      <c r="W36" s="6">
+        <v>-0.003716864810060342</v>
+      </c>
+      <c r="X36" s="8">
+        <v>22.695834999999999</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>5.274443333333334</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>3.0108350000000002</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>8.1091660000000001</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>15.059999999999999</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.94999999999999996</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7881,7 +7951,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7917,25 +7987,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>1234</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1234</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>0.035321755180803605</v>
+      </c>
+      <c r="R51" s="7">
+        <v>9</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.18181818181818177</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.33984602917341977</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.030899513776337116</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.072836304700162072</v>
+      </c>
+      <c r="X51" s="8">
+        <v>31.133328571428571</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>4.957411111111111</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>14.011899999999999</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>19.419046000000002</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>26.349999999999998</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.42857142857142855</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -12636,7 +12742,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12675,7 +12781,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12709,25 +12815,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>4038.7800000000002</v>
+      </c>
+      <c r="P89" s="5">
+        <v>4038.7800000000002</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.42183628157061803</v>
+      </c>
+      <c r="R89" s="7">
+        <v>43</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.42666666666666664</v>
+      </c>
+      <c r="T89" s="6">
+        <v>-0.94129014207260597</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-1.3107754817048711</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.035895121794205176</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.011479332867846229</v>
+      </c>
+      <c r="X89" s="8">
+        <v>30.944869230769232</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>3.8601634146341461</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>8.375</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>19.193592307692306</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.53846153846153844</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -15487,7 +15627,7 @@
         <v>0</v>
       </c>
       <c r="AH111" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI111" s="11"/>
       <c r="AJ111" s="13">
@@ -15840,7 +15980,7 @@
         <v>-100.5</v>
       </c>
       <c r="AH114" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI114" s="11"/>
       <c r="AJ114" s="13">
@@ -16715,7 +16855,7 @@
         <v>0</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -16977,7 +17117,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17370,7 +17510,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18547,7 +18687,7 @@
         <v>0</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -18678,7 +18818,7 @@
         <v>-520.60000000000002</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20865,7 +21005,7 @@
         <v>-1073.3599999999999</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -20992,7 +21132,7 @@
         <v>15</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -22147,7 +22287,7 @@
         <v>-1672.6900000000001</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -24225,7 +24365,9 @@
       <c r="AB179" s="8">
         <v>1.2566679999999999</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>4.4379989999999996</v>
+      </c>
       <c r="AD179" s="8">
         <v>11.375999999999999</v>
       </c>
@@ -28310,7 +28452,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>
